--- a/20240307_histogram_test/output/20240307_histogram_test_element_pairs.xlsx
+++ b/20240307_histogram_test/output/20240307_histogram_test_element_pairs.xlsx
@@ -1,73 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Si" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ru-Ge" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ge" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sb" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sb-Sb" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Pt" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Sb" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Si" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Fe" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-Si" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Y-Fe" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Y-Si" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Ge" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Si" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ni" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Si" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ni" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ni" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ga" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ga" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-Pd" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Pd" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-In" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ge" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yb-Ge" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Fe" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Ga" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Ga" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Dy" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-Si" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Si" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Pd" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-In" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Ge" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Ge" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Ge" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Ge" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Sb" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tb-Ge" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Ni" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-In" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Si" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Ni" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Si" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ge" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Si" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Fe" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ir-Ge" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ge" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="Rh-Si" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rh-Rh" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ru-Ge" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ge-Ge" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="La-Ge" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Pt-Sb" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sb-Sb" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="La-Sb" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="La-Pt" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Pt-Pt" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Fe-Si" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Fe-Fe" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Si-Si" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Y-Si" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Y-Fe" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Rh-Ge" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Dy-Ge" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Ni-Si" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Ni-Ni" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Pr-Ni" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Pr-Si" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Ga-Ga" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Ni-Ga" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Ce-Ga" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Ce-Ni" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Pd-Pd" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Ce-Pd" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Pd-In" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Co-Ge" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Yb-Ge" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Fe-Ga" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Dy-Fe" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Dy-Ga" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Dy-Dy" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="Pd-Si" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="Lu-Si" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="Lu-Pd" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="Er-Co" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Er-In" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="In-In" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="Lu-Ge" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="Fe-Ge" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="Gd-Ge" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="Er-Ge" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="Ho-Ge" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="Ni-Sb" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="Tb-Ge" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="Er-Ni" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="Ni-In" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="Sm-Ge" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="Nd-Ge" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="Gd-Si" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="Gd-Ni" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="Eu-Si" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="Pr-Ge" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="Ce-Si" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="Ce-Fe" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="Ir-Ge" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet name="Eu-Ge" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet name="Ce-Ge" sheetId="60" state="visible" r:id="rId60"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -583,7 +582,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.14</v>
+        <v>2.727</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -603,7 +602,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.14</v>
+        <v>2.727</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -1838,6 +1837,285 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301489.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.314</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1942974.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.426</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301489.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.546</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.497</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301489.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.242</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.231</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1897,285 +2175,6 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301489.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.242</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.231</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.449</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301489.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.546</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.497</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301489.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.314</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.449</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1942974.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.514</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.426</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3384,7 +3383,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.051</v>
+        <v>2.644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3404,7 +3403,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.051</v>
+        <v>2.644</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -3455,7 +3454,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.644</v>
+        <v>3.024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3475,7 +3474,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.644</v>
+        <v>3.024</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -3499,6 +3498,244 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300164.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.236</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300170.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300169.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>554324.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.302</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300157.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.317</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.323</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.329</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.352</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.359</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>300171.cif</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.396</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.317</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3522,11 +3759,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300169.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.241</v>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.999</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3546,7 +3783,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.241</v>
+        <v>2.999</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -3564,7 +3801,95 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301180.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.197</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301180 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.197</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.197</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3593,15 +3918,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.999</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
+          <t>554324.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.302</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3942,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.999</v>
+        <v>2.302</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -3635,7 +3960,286 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301181.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301181 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300164.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.194</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.869</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301183.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301183 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301184 2.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301184.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3664,15 +4268,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.975</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
+          <t>529848.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.531</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -3688,7 +4292,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.975</v>
+        <v>2.531</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -3706,516 +4310,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301180.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.197</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301180 2.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.197</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.197</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>554324.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.302</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.302</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301181.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.207</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301181 2.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.207</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300164.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.194</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1.869</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.147</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301183.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301183 2.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301184 2.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301184.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>529848.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.531</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.531</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4333,7 +4428,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4404,245 +4499,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300163.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.233</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300164.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300170.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300169.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>554324.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.302</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>300157.cif</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.317</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.323</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.329</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.352</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>300162.cif</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.359</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>300171.cif</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.383</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.396</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.317</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4713,7 +4570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4742,11 +4599,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.141</v>
+          <t>300169.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4766,7 +4623,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.141</v>
+        <v>3.241</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -4784,7 +4641,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4813,11 +4670,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.157</v>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4837,7 +4694,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.157</v>
+        <v>3.141</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -4855,7 +4712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4884,15 +4741,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301531.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.063</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.157</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4765,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.063</v>
+        <v>3.157</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -4926,7 +4783,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4997,7 +4854,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5026,15 +4883,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300808.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.125</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
+          <t>301531.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.063</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -5050,7 +4907,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.125</v>
+        <v>3.063</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5068,7 +4925,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5097,11 +4954,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300162.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.161</v>
+          <t>300808.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5121,7 +4978,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.161</v>
+        <v>3.125</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5139,7 +4996,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5168,15 +5025,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301697.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.146</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.161</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5049,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.146</v>
+        <v>3.161</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5210,7 +5067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5281,7 +5138,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5310,15 +5167,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300171.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.537</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
+          <t>301697.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.146</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5191,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.537</v>
+        <v>3.146</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5352,7 +5209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5381,15 +5238,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300237.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.727</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>300171.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.537</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5262,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.727</v>
+        <v>2.537</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5423,7 +5280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5511,7 +5368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5540,15 +5397,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300170.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.227</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
+          <t>300237.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5421,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.227</v>
+        <v>2.727</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5582,7 +5439,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5611,15 +5468,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300237.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.727</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>300170.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.227</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5492,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.727</v>
+        <v>3.227</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5653,7 +5510,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5741,7 +5598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5810,4 +5667,75 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300237.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/20240307_histogram_test/output/20240307_histogram_test_element_pairs.xlsx
+++ b/20240307_histogram_test/output/20240307_histogram_test_element_pairs.xlsx
@@ -1,72 +1,73 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rh-Si" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Rh-Rh" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ru-Ge" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Ge-Ge" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="La-Ge" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Pt-Sb" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sb-Sb" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="La-Sb" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="La-Pt" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Pt-Pt" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Fe-Si" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Fe-Fe" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Si-Si" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Y-Si" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Y-Fe" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Rh-Ge" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Dy-Ge" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Ni-Si" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Ni-Ni" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Pr-Ni" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Pr-Si" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Ga-Ga" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Ni-Ga" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Ce-Ga" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Ce-Ni" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Pd-Pd" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Ce-Pd" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Pd-In" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Co-Ge" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Yb-Ge" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="Fe-Ga" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="Dy-Fe" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="Dy-Ga" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="Dy-Dy" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="Pd-Si" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="Lu-Si" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="Lu-Pd" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="Er-Co" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="Er-In" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="In-In" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="Lu-Ge" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="Fe-Ge" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="Gd-Ge" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet name="Er-Ge" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet name="Ho-Ge" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="Ni-Sb" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="Tb-Ge" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet name="Er-Ni" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet name="Ni-In" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet name="Sm-Ge" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet name="Nd-Ge" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="Gd-Si" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="Gd-Ni" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet name="Eu-Si" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet name="Pr-Ge" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet name="Ce-Si" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet name="Ce-Fe" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet name="Ir-Ge" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet name="Eu-Ge" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet name="Ce-Ge" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Si" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ru-Ge" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ge" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sb" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sb-Sb" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Sb" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Pt" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Si" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-Si" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Fe" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Y-Fe" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Y-Si" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Ge" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ni" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Si" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ni" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Si" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ga" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ni" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ga" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Pd" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-Pd" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-In" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ge" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yb-Ge" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Ga" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Ga" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Fe" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Dy" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-Si" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Si" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Pd" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-In" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Ge" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Ge" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Ge" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Ge" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Sb" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tb-Ge" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Ni" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-In" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Ni" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Si" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Si" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ge" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Fe" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Si" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ir-Ge" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ge" sheetId="61" state="visible" r:id="rId61"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -511,11 +512,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
+        <v>2.524</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -531,7 +532,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.28</v>
+        <v>2.524</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -582,7 +583,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.727</v>
+        <v>3.14</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.727</v>
+        <v>3.14</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -724,6 +725,169 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300808.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301710.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.293</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>301531.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1940621.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1955459.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.328</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>301697.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1617211.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.354</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -841,169 +1005,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300808.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.175</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301710.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.293</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>301531.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1940621.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.325</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1955459.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.328</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>301697.cif</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1617211.cif</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.354</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.305</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1403,109 +1404,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301531.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1955459.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.328</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300808.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.456</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.366</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1618,6 +1516,109 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301531.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1955459.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.328</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300808.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.456</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.366</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1651,11 +1652,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.524</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
+        <v>2.28</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1672,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.524</v>
+        <v>2.28</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -1837,6 +1838,253 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301489.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.242</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.231</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.242</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.242</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301489.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.546</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.497</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1934,7 +2182,78 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1949113.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.033</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.033</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1963,30 +2282,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.449</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>1940621.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301489.cif</t>
+          <t>1949113.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.546</v>
+        <v>2.431</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Deficiency without atomic mixing</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2321,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.497</v>
+        <v>2.378</v>
       </c>
       <c r="C5" t="inlineStr"/>
     </row>
@@ -2013,327 +2332,9 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="C6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301489.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.242</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.231</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.242</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.242</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1940621.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.325</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1949113.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1949113.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.033</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.033</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3454,7 +3455,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.024</v>
+        <v>3.051</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3474,7 +3475,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.024</v>
+        <v>3.051</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -3763,7 +3764,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.999</v>
+        <v>2.975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3783,7 +3784,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.999</v>
+        <v>2.975</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -3802,6 +3803,77 @@
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.999</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.999</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3889,7 +3961,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3960,7 +4032,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4063,7 +4135,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4151,7 +4223,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4239,7 +4311,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4310,7 +4382,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4428,7 +4500,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4499,7 +4571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4528,15 +4600,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1910757.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.886</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
+          <t>300169.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.241</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4624,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.886</v>
+        <v>3.241</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -4570,7 +4642,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4599,15 +4671,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300169.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.241</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
+          <t>1910757.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.886</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4695,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.241</v>
+        <v>2.886</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -4641,7 +4713,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4712,7 +4784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4783,7 +4855,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4854,7 +4926,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4925,7 +4997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4996,7 +5068,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5067,7 +5139,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5138,7 +5210,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5209,7 +5281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5280,7 +5352,78 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300237.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5368,7 +5511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5397,15 +5540,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300237.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.727</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>300170.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.227</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5564,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.727</v>
+        <v>3.227</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5439,7 +5582,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5468,15 +5611,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300170.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.227</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
+          <t>300237.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5635,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.227</v>
+        <v>2.727</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5510,7 +5653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5598,7 +5741,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5667,75 +5810,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300237.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>